--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:37</t>
+    <t xml:space="preserve">2026-09-09 19:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:56</t>
+    <t xml:space="preserve">2026-09-18 17:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
@@ -30,33 +30,33 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocopilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro de Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro de Atacama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antofagasta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tocopilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mejillones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:02</t>
+    <t xml:space="preserve">2026-09-27 21:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -486,13 +486,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4747</v>
+        <v>14284</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6749</v>
+        <v>14143</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>70.34</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
@@ -500,13 +500,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>205</v>
+        <v>27032</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>284</v>
+        <v>27659</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>72.18</v>
+        <v>97.73</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1309</v>
+        <v>179471</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1690</v>
+        <v>184036</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>77.46</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="5">
@@ -528,13 +528,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8394</v>
+        <v>12721</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10013</v>
+        <v>13371</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>83.83</v>
+        <v>95.14</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>12721</v>
+        <v>8394</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>13371</v>
+        <v>10013</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>95.14</v>
+        <v>83.83</v>
       </c>
     </row>
     <row r="8">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>179471</v>
+        <v>1309</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>184036</v>
+        <v>1690</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>97.52</v>
+        <v>77.46</v>
       </c>
     </row>
     <row r="9">
@@ -584,13 +584,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>27032</v>
+        <v>205</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>27659</v>
+        <v>284</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>97.73</v>
+        <v>72.18</v>
       </c>
     </row>
     <row r="10">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>14284</v>
+        <v>4747</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>14143</v>
+        <v>6749</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>101</v>
+        <v>70.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:44</t>
+    <t xml:space="preserve">2026-10-05 05:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
